--- a/IN_year1_awardees.xlsx
+++ b/IN_year1_awardees.xlsx
@@ -224,7 +224,7 @@
     <t xml:space="preserve">NOTICE_OF_INTENT_TO_AWARD</t>
   </si>
   <si>
-    <t xml:space="preserve">PARSED_FROM_PDF</t>
+    <t xml:space="preserve">DIRECT_TEXT</t>
   </si>
   <si>
     <t xml:space="preserve">R/03s_in_year1_awardees.R</t>
